--- a/output/StructureDefinition-BRConjuntoMinimoDados-1.1.xlsx
+++ b/output/StructureDefinition-BRConjuntoMinimoDados-1.1.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7536" uniqueCount="739">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7534" uniqueCount="747">
   <si>
     <t>Property</t>
   </si>
@@ -911,6 +911,15 @@
     <t>gender</t>
   </si>
   <si>
+    <t>Sexo</t>
+  </si>
+  <si>
+    <t>Sexo biológico obtido por meio de exame clínico ou de outros métodos diagnósticos referente ao indivíduo da hipótese de impossibilidade de identificação.</t>
+  </si>
+  <si>
+    <t>http://www.saude.gov.br/fhir/r4/ValueSet/BRSexo-1.0</t>
+  </si>
+  <si>
     <t>Composition.subject.extension:unidentifiedPatient.extension:gender.id</t>
   </si>
   <si>
@@ -960,6 +969,12 @@
   </si>
   <si>
     <t>birthYear</t>
+  </si>
+  <si>
+    <t>Ano de nascimento estimado</t>
+  </si>
+  <si>
+    <t>Estimativa do ano de nascimento por meio de observação direta da idade do indivíduo na hipótese de impossibilidade de identificação..</t>
   </si>
   <si>
     <t>Composition.subject.extension:unidentifiedPatient.extension:birthYear.id</t>
@@ -982,6 +997,15 @@
   </si>
   <si>
     <t>reason</t>
+  </si>
+  <si>
+    <t>Justificativa da impossibilidade de identificação do indivíduo</t>
+  </si>
+  <si>
+    <t>Razão pela qual não foi possível obter os dados de identificação do indivíduo no contato assistencial.</t>
+  </si>
+  <si>
+    <t>http://www.saude.gov.br/fhir/r4/ValueSet/BRJustificativaIndividuoNaoIdentificado-1.0</t>
   </si>
   <si>
     <t>Composition.subject.extension:unidentifiedPatient.extension:reason.id</t>
@@ -2633,7 +2657,7 @@
     <col min="23" max="23" width="16.40625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="15.85546875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="87.265625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="66.109375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="71.20703125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.2734375" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.1484375" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.56640625" customWidth="true" bestFit="true"/>
@@ -7615,10 +7639,10 @@
         <v>137</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7645,13 +7669,11 @@
         <v>82</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y43" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="Y43" s="2"/>
       <c r="Z43" t="s" s="2">
-        <v>82</v>
+        <v>291</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>82</v>
@@ -7701,10 +7723,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7816,10 +7838,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7933,10 +7955,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7962,13 +7984,13 @@
         <v>105</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -8018,7 +8040,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>92</v>
@@ -8050,10 +8072,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8079,10 +8101,10 @@
         <v>111</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -8133,7 +8155,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -8165,13 +8187,13 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="B48" t="s" s="2">
         <v>283</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="D48" t="s" s="2">
         <v>82</v>
@@ -8196,10 +8218,10 @@
         <v>137</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>285</v>
+        <v>309</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>286</v>
+        <v>310</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -8282,10 +8304,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8397,10 +8419,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8514,10 +8536,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8543,13 +8565,13 @@
         <v>105</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8557,7 +8579,7 @@
       </c>
       <c r="Q51" s="2"/>
       <c r="R51" t="s" s="2">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="S51" t="s" s="2">
         <v>82</v>
@@ -8599,7 +8621,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>92</v>
@@ -8631,10 +8653,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8657,13 +8679,13 @@
         <v>82</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8714,7 +8736,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -8746,13 +8768,13 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="B53" t="s" s="2">
         <v>283</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="D53" t="s" s="2">
         <v>82</v>
@@ -8777,10 +8799,10 @@
         <v>137</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>285</v>
+        <v>318</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>286</v>
+        <v>319</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8807,13 +8829,11 @@
         <v>82</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y53" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="Y53" s="2"/>
       <c r="Z53" t="s" s="2">
-        <v>82</v>
+        <v>320</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>82</v>
@@ -8863,10 +8883,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8978,10 +8998,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9095,10 +9115,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9124,13 +9144,13 @@
         <v>105</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9138,7 +9158,7 @@
       </c>
       <c r="Q56" s="2"/>
       <c r="R56" t="s" s="2">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="S56" t="s" s="2">
         <v>82</v>
@@ -9180,7 +9200,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>92</v>
@@ -9212,10 +9232,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9241,10 +9261,10 @@
         <v>172</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -9295,7 +9315,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -9327,10 +9347,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9356,13 +9376,13 @@
         <v>105</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9370,7 +9390,7 @@
       </c>
       <c r="Q58" s="2"/>
       <c r="R58" t="s" s="2">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="S58" t="s" s="2">
         <v>82</v>
@@ -9412,7 +9432,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>92</v>
@@ -9444,10 +9464,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9470,13 +9490,13 @@
         <v>82</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9527,7 +9547,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -9559,10 +9579,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9588,13 +9608,13 @@
         <v>184</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9644,7 +9664,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -9653,7 +9673,7 @@
         <v>92</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>103</v>
@@ -9676,10 +9696,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9705,13 +9725,13 @@
         <v>105</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9719,7 +9739,7 @@
       </c>
       <c r="Q61" s="2"/>
       <c r="R61" t="s" s="2">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="S61" t="s" s="2">
         <v>82</v>
@@ -9737,13 +9757,13 @@
         <v>82</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>82</v>
@@ -9761,7 +9781,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -9793,10 +9813,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9822,13 +9842,13 @@
         <v>149</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9878,7 +9898,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -9896,7 +9916,7 @@
         <v>82</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>82</v>
@@ -9910,10 +9930,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10025,10 +10045,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10142,10 +10162,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10171,16 +10191,16 @@
         <v>111</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>82</v>
@@ -10208,10 +10228,10 @@
         <v>163</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>82</v>
@@ -10229,7 +10249,7 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -10247,7 +10267,7 @@
         <v>82</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>82</v>
@@ -10261,10 +10281,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10290,16 +10310,16 @@
         <v>172</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>82</v>
@@ -10324,13 +10344,13 @@
         <v>82</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>82</v>
@@ -10348,7 +10368,7 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -10366,7 +10386,7 @@
         <v>82</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>82</v>
@@ -10380,10 +10400,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10409,16 +10429,16 @@
         <v>105</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>82</v>
@@ -10431,7 +10451,7 @@
         <v>82</v>
       </c>
       <c r="T67" t="s" s="2">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="U67" t="s" s="2">
         <v>82</v>
@@ -10467,7 +10487,7 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -10485,7 +10505,7 @@
         <v>82</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>82</v>
@@ -10499,10 +10519,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10528,13 +10548,13 @@
         <v>184</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10548,7 +10568,7 @@
         <v>82</v>
       </c>
       <c r="T68" t="s" s="2">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="U68" t="s" s="2">
         <v>82</v>
@@ -10584,7 +10604,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -10602,7 +10622,7 @@
         <v>82</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>82</v>
@@ -10616,10 +10636,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10642,13 +10662,13 @@
         <v>81</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10699,7 +10719,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -10717,7 +10737,7 @@
         <v>82</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>82</v>
@@ -10731,10 +10751,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10757,16 +10777,16 @@
         <v>81</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10816,7 +10836,7 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -10834,7 +10854,7 @@
         <v>82</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>82</v>
@@ -10848,10 +10868,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10877,13 +10897,13 @@
         <v>184</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10933,7 +10953,7 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10965,10 +10985,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10991,17 +11011,17 @@
         <v>81</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" t="s" s="2">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>82</v>
@@ -11050,7 +11070,7 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -11065,27 +11085,27 @@
         <v>103</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>405</v>
+        <v>413</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11108,19 +11128,19 @@
         <v>81</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>82</v>
@@ -11169,7 +11189,7 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>92</v>
@@ -11184,27 +11204,27 @@
         <v>103</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>413</v>
+        <v>421</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>416</v>
+        <v>424</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11227,19 +11247,19 @@
         <v>81</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>418</v>
+        <v>426</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>82</v>
@@ -11288,7 +11308,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>92</v>
@@ -11303,27 +11323,27 @@
         <v>103</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>427</v>
+        <v>435</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11435,10 +11455,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11552,10 +11572,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11581,13 +11601,13 @@
         <v>184</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -11637,7 +11657,7 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
@@ -11646,7 +11666,7 @@
         <v>92</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="AJ77" t="s" s="2">
         <v>103</v>
@@ -11669,10 +11689,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>431</v>
+        <v>439</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>431</v>
+        <v>439</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11698,13 +11718,13 @@
         <v>105</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -11730,13 +11750,13 @@
         <v>82</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>82</v>
@@ -11754,7 +11774,7 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
@@ -11786,10 +11806,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11815,13 +11835,13 @@
         <v>149</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -11871,7 +11891,7 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
@@ -11889,7 +11909,7 @@
         <v>82</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>82</v>
@@ -11903,10 +11923,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12018,10 +12038,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>434</v>
+        <v>442</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>434</v>
+        <v>442</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12135,10 +12155,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12164,16 +12184,16 @@
         <v>111</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>82</v>
@@ -12201,10 +12221,10 @@
         <v>163</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>82</v>
@@ -12222,7 +12242,7 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>79</v>
@@ -12240,7 +12260,7 @@
         <v>82</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>82</v>
@@ -12254,10 +12274,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12283,16 +12303,16 @@
         <v>172</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>82</v>
@@ -12317,13 +12337,13 @@
         <v>82</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>82</v>
@@ -12341,7 +12361,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
@@ -12359,7 +12379,7 @@
         <v>82</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>82</v>
@@ -12373,10 +12393,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12402,16 +12422,16 @@
         <v>105</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>82</v>
@@ -12424,7 +12444,7 @@
         <v>82</v>
       </c>
       <c r="T84" t="s" s="2">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="U84" t="s" s="2">
         <v>82</v>
@@ -12460,7 +12480,7 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
@@ -12478,7 +12498,7 @@
         <v>82</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>82</v>
@@ -12492,10 +12512,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12521,13 +12541,13 @@
         <v>184</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12541,7 +12561,7 @@
         <v>82</v>
       </c>
       <c r="T85" t="s" s="2">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="U85" t="s" s="2">
         <v>82</v>
@@ -12577,7 +12597,7 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>79</v>
@@ -12595,7 +12615,7 @@
         <v>82</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>82</v>
@@ -12609,10 +12629,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12635,13 +12655,13 @@
         <v>81</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -12692,7 +12712,7 @@
         <v>82</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>
@@ -12710,7 +12730,7 @@
         <v>82</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>82</v>
@@ -12724,10 +12744,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12750,16 +12770,16 @@
         <v>81</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -12809,7 +12829,7 @@
         <v>82</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>79</v>
@@ -12827,7 +12847,7 @@
         <v>82</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>82</v>
@@ -12841,10 +12861,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12870,13 +12890,13 @@
         <v>184</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -12926,7 +12946,7 @@
         <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>79</v>
@@ -12958,10 +12978,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12987,13 +13007,13 @@
         <v>184</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -13043,7 +13063,7 @@
         <v>82</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>92</v>
@@ -13061,13 +13081,13 @@
         <v>82</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>82</v>
@@ -13075,10 +13095,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>449</v>
+        <v>457</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>449</v>
+        <v>457</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13104,13 +13124,13 @@
         <v>111</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -13139,10 +13159,10 @@
         <v>163</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>82</v>
@@ -13160,7 +13180,7 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>449</v>
+        <v>457</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>79</v>
@@ -13178,13 +13198,13 @@
         <v>82</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>456</v>
+        <v>464</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>82</v>
@@ -13192,10 +13212,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13218,19 +13238,19 @@
         <v>82</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>462</v>
+        <v>470</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>82</v>
@@ -13279,7 +13299,7 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>79</v>
@@ -13297,13 +13317,13 @@
         <v>82</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>82</v>
@@ -13311,10 +13331,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>466</v>
+        <v>474</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>466</v>
+        <v>474</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13426,10 +13446,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13543,14 +13563,14 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>468</v>
+        <v>476</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>468</v>
+        <v>476</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
@@ -13572,10 +13592,10 @@
         <v>137</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>470</v>
+        <v>478</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>471</v>
+        <v>479</v>
       </c>
       <c r="N94" t="s" s="2">
         <v>140</v>
@@ -13630,7 +13650,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>472</v>
+        <v>480</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>79</v>
@@ -13662,10 +13682,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13691,14 +13711,14 @@
         <v>111</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>474</v>
+        <v>482</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>475</v>
+        <v>483</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" t="s" s="2">
-        <v>476</v>
+        <v>484</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>82</v>
@@ -13726,10 +13746,10 @@
         <v>163</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="Z95" t="s" s="2">
-        <v>478</v>
+        <v>486</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>82</v>
@@ -13747,7 +13767,7 @@
         <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>92</v>
@@ -13765,10 +13785,10 @@
         <v>82</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="AN95" t="s" s="2">
         <v>82</v>
@@ -13779,10 +13799,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13805,17 +13825,17 @@
         <v>82</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>482</v>
+        <v>490</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>483</v>
+        <v>491</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" t="s" s="2">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>82</v>
@@ -13864,7 +13884,7 @@
         <v>82</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>79</v>
@@ -13882,10 +13902,10 @@
         <v>82</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>486</v>
+        <v>494</v>
       </c>
       <c r="AN96" t="s" s="2">
         <v>82</v>
@@ -13896,10 +13916,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>487</v>
+        <v>495</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>487</v>
+        <v>495</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13922,17 +13942,17 @@
         <v>82</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>488</v>
+        <v>496</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>489</v>
+        <v>497</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>490</v>
+        <v>498</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" t="s" s="2">
-        <v>491</v>
+        <v>499</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>82</v>
@@ -13981,7 +14001,7 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>487</v>
+        <v>495</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>79</v>
@@ -13999,24 +14019,24 @@
         <v>82</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>492</v>
+        <v>500</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>493</v>
+        <v>501</v>
       </c>
       <c r="AN97" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>494</v>
+        <v>502</v>
       </c>
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14039,19 +14059,19 @@
         <v>81</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>496</v>
+        <v>504</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>497</v>
+        <v>505</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>498</v>
+        <v>506</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>499</v>
+        <v>507</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>82</v>
@@ -14100,7 +14120,7 @@
         <v>82</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>79</v>
@@ -14118,13 +14138,13 @@
         <v>82</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>500</v>
+        <v>508</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>501</v>
+        <v>509</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>502</v>
+        <v>510</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>82</v>
@@ -14132,10 +14152,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>503</v>
+        <v>511</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>503</v>
+        <v>511</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14158,19 +14178,19 @@
         <v>82</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>504</v>
+        <v>512</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>505</v>
+        <v>513</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>506</v>
+        <v>514</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>507</v>
+        <v>515</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>82</v>
@@ -14219,7 +14239,7 @@
         <v>82</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>503</v>
+        <v>511</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>79</v>
@@ -14237,13 +14257,13 @@
         <v>82</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>508</v>
+        <v>516</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>509</v>
+        <v>517</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>510</v>
+        <v>518</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>82</v>
@@ -14251,10 +14271,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14366,10 +14386,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>512</v>
+        <v>520</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>512</v>
+        <v>520</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14483,14 +14503,14 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>513</v>
+        <v>521</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>513</v>
+        <v>521</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
@@ -14512,10 +14532,10 @@
         <v>137</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>470</v>
+        <v>478</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>471</v>
+        <v>479</v>
       </c>
       <c r="N102" t="s" s="2">
         <v>140</v>
@@ -14570,7 +14590,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>472</v>
+        <v>480</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>79</v>
@@ -14602,10 +14622,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>514</v>
+        <v>522</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>514</v>
+        <v>522</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14631,23 +14651,23 @@
         <v>111</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>515</v>
+        <v>523</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>516</v>
+        <v>524</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>517</v>
+        <v>525</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q103" s="2"/>
       <c r="R103" t="s" s="2">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="S103" t="s" s="2">
         <v>82</v>
@@ -14668,10 +14688,10 @@
         <v>163</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>521</v>
+        <v>529</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>82</v>
@@ -14689,7 +14709,7 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>514</v>
+        <v>522</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>92</v>
@@ -14707,13 +14727,13 @@
         <v>82</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>522</v>
+        <v>530</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>523</v>
+        <v>531</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>524</v>
+        <v>532</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>82</v>
@@ -14721,10 +14741,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>525</v>
+        <v>533</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>525</v>
+        <v>533</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14747,17 +14767,17 @@
         <v>82</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>526</v>
+        <v>534</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>527</v>
+        <v>535</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" t="s" s="2">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>82</v>
@@ -14806,7 +14826,7 @@
         <v>82</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>525</v>
+        <v>533</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>92</v>
@@ -14824,13 +14844,13 @@
         <v>82</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>530</v>
+        <v>538</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>531</v>
+        <v>539</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>82</v>
@@ -14838,10 +14858,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>532</v>
+        <v>540</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>532</v>
+        <v>540</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14953,10 +14973,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>533</v>
+        <v>541</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>533</v>
+        <v>541</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15070,10 +15090,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>534</v>
+        <v>542</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>534</v>
+        <v>542</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15099,13 +15119,13 @@
         <v>184</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
@@ -15155,7 +15175,7 @@
         <v>82</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>79</v>
@@ -15164,7 +15184,7 @@
         <v>92</v>
       </c>
       <c r="AI107" t="s" s="2">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="AJ107" t="s" s="2">
         <v>103</v>
@@ -15187,10 +15207,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>535</v>
+        <v>543</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>535</v>
+        <v>543</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15216,13 +15236,13 @@
         <v>105</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -15248,13 +15268,13 @@
         <v>82</v>
       </c>
       <c r="X108" t="s" s="2">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="Y108" t="s" s="2">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="Z108" t="s" s="2">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>82</v>
@@ -15272,7 +15292,7 @@
         <v>82</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>79</v>
@@ -15304,10 +15324,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>536</v>
+        <v>544</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>536</v>
+        <v>544</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15333,13 +15353,13 @@
         <v>149</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
@@ -15389,7 +15409,7 @@
         <v>82</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>79</v>
@@ -15407,7 +15427,7 @@
         <v>82</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="AM109" t="s" s="2">
         <v>82</v>
@@ -15421,10 +15441,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15450,13 +15470,13 @@
         <v>184</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -15506,7 +15526,7 @@
         <v>82</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>79</v>
@@ -15538,10 +15558,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>538</v>
+        <v>546</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>538</v>
+        <v>546</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15564,19 +15584,19 @@
         <v>81</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>539</v>
+        <v>547</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>540</v>
+        <v>548</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>541</v>
+        <v>549</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>542</v>
+        <v>550</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>82</v>
@@ -15625,7 +15645,7 @@
         <v>82</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>538</v>
+        <v>546</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>79</v>
@@ -15643,13 +15663,13 @@
         <v>82</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>543</v>
+        <v>551</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>544</v>
+        <v>552</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>545</v>
+        <v>553</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>82</v>
@@ -15657,10 +15677,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>546</v>
+        <v>554</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>546</v>
+        <v>554</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15772,10 +15792,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>547</v>
+        <v>555</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>547</v>
+        <v>555</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15889,14 +15909,14 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>548</v>
+        <v>556</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>548</v>
+        <v>556</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
@@ -15918,10 +15938,10 @@
         <v>137</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>470</v>
+        <v>478</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>471</v>
+        <v>479</v>
       </c>
       <c r="N114" t="s" s="2">
         <v>140</v>
@@ -15976,7 +15996,7 @@
         <v>82</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>472</v>
+        <v>480</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>79</v>
@@ -16008,10 +16028,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>549</v>
+        <v>557</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>549</v>
+        <v>557</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16037,13 +16057,13 @@
         <v>172</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>550</v>
+        <v>558</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>551</v>
+        <v>559</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>552</v>
+        <v>560</v>
       </c>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
@@ -16069,13 +16089,13 @@
         <v>82</v>
       </c>
       <c r="X115" t="s" s="2">
-        <v>553</v>
+        <v>561</v>
       </c>
       <c r="Y115" t="s" s="2">
-        <v>554</v>
+        <v>562</v>
       </c>
       <c r="Z115" t="s" s="2">
-        <v>555</v>
+        <v>563</v>
       </c>
       <c r="AA115" t="s" s="2">
         <v>82</v>
@@ -16093,7 +16113,7 @@
         <v>82</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>549</v>
+        <v>557</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>79</v>
@@ -16117,7 +16137,7 @@
         <v>180</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>556</v>
+        <v>564</v>
       </c>
       <c r="AO115" t="s" s="2">
         <v>82</v>
@@ -16125,10 +16145,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>557</v>
+        <v>565</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>557</v>
+        <v>565</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16151,13 +16171,13 @@
         <v>81</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>558</v>
+        <v>566</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>559</v>
+        <v>567</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
@@ -16208,7 +16228,7 @@
         <v>82</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>557</v>
+        <v>565</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>79</v>
@@ -16226,13 +16246,13 @@
         <v>82</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="AN116" t="s" s="2">
-        <v>560</v>
+        <v>568</v>
       </c>
       <c r="AO116" t="s" s="2">
         <v>82</v>
@@ -16240,10 +16260,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>561</v>
+        <v>569</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>561</v>
+        <v>569</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16266,13 +16286,13 @@
         <v>81</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>562</v>
+        <v>570</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>563</v>
+        <v>571</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>564</v>
+        <v>572</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
@@ -16323,7 +16343,7 @@
         <v>82</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>561</v>
+        <v>569</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>79</v>
@@ -16341,7 +16361,7 @@
         <v>82</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>565</v>
+        <v>573</v>
       </c>
       <c r="AM117" t="s" s="2">
         <v>168</v>
@@ -16355,10 +16375,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>566</v>
+        <v>574</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>566</v>
+        <v>574</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16381,13 +16401,13 @@
         <v>82</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>567</v>
+        <v>575</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>568</v>
+        <v>576</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
@@ -16426,7 +16446,7 @@
         <v>82</v>
       </c>
       <c r="AB118" t="s" s="2">
-        <v>569</v>
+        <v>577</v>
       </c>
       <c r="AC118" s="2"/>
       <c r="AD118" t="s" s="2">
@@ -16436,7 +16456,7 @@
         <v>192</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>566</v>
+        <v>574</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>79</v>
@@ -16448,16 +16468,16 @@
         <v>82</v>
       </c>
       <c r="AJ118" t="s" s="2">
-        <v>570</v>
+        <v>578</v>
       </c>
       <c r="AK118" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL118" t="s" s="2">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="AM118" t="s" s="2">
-        <v>572</v>
+        <v>580</v>
       </c>
       <c r="AN118" t="s" s="2">
         <v>82</v>
@@ -16468,10 +16488,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>573</v>
+        <v>581</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>573</v>
+        <v>581</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16583,10 +16603,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16700,14 +16720,14 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>575</v>
+        <v>583</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>575</v>
+        <v>583</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E121" s="2"/>
       <c r="F121" t="s" s="2">
@@ -16729,10 +16749,10 @@
         <v>137</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>470</v>
+        <v>478</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>471</v>
+        <v>479</v>
       </c>
       <c r="N121" t="s" s="2">
         <v>140</v>
@@ -16787,7 +16807,7 @@
         <v>82</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>472</v>
+        <v>480</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>79</v>
@@ -16819,14 +16839,14 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>576</v>
+        <v>584</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>576</v>
+        <v>584</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
-        <v>577</v>
+        <v>585</v>
       </c>
       <c r="E122" s="2"/>
       <c r="F122" t="s" s="2">
@@ -16848,16 +16868,16 @@
         <v>184</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>578</v>
+        <v>586</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>579</v>
+        <v>587</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>580</v>
+        <v>588</v>
       </c>
       <c r="O122" t="s" s="2">
-        <v>581</v>
+        <v>589</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>82</v>
@@ -16906,7 +16926,7 @@
         <v>82</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>576</v>
+        <v>584</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>79</v>
@@ -16924,10 +16944,10 @@
         <v>82</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="AN122" t="s" s="2">
         <v>82</v>
@@ -16938,10 +16958,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>582</v>
+        <v>590</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>582</v>
+        <v>590</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16967,16 +16987,16 @@
         <v>172</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>583</v>
+        <v>591</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>584</v>
+        <v>592</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="O123" t="s" s="2">
-        <v>586</v>
+        <v>594</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>82</v>
@@ -17001,13 +17021,13 @@
         <v>82</v>
       </c>
       <c r="X123" t="s" s="2">
-        <v>553</v>
+        <v>561</v>
       </c>
       <c r="Y123" t="s" s="2">
-        <v>587</v>
+        <v>595</v>
       </c>
       <c r="Z123" t="s" s="2">
-        <v>588</v>
+        <v>596</v>
       </c>
       <c r="AA123" t="s" s="2">
         <v>82</v>
@@ -17025,7 +17045,7 @@
         <v>82</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>582</v>
+        <v>590</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>79</v>
@@ -17057,10 +17077,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>589</v>
+        <v>597</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>589</v>
+        <v>597</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17083,17 +17103,17 @@
         <v>82</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>590</v>
+        <v>598</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>591</v>
+        <v>599</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>592</v>
+        <v>600</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" t="s" s="2">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>82</v>
@@ -17142,7 +17162,7 @@
         <v>82</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>589</v>
+        <v>597</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>79</v>
@@ -17160,24 +17180,24 @@
         <v>82</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="AM124" t="s" s="2">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="AN124" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO124" t="s" s="2">
-        <v>427</v>
+        <v>435</v>
       </c>
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>593</v>
+        <v>601</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>593</v>
+        <v>601</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17200,16 +17220,16 @@
         <v>82</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>562</v>
+        <v>570</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>594</v>
+        <v>602</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>595</v>
+        <v>603</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>596</v>
+        <v>604</v>
       </c>
       <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
@@ -17259,7 +17279,7 @@
         <v>82</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>593</v>
+        <v>601</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>79</v>
@@ -17280,7 +17300,7 @@
         <v>82</v>
       </c>
       <c r="AM125" t="s" s="2">
-        <v>597</v>
+        <v>605</v>
       </c>
       <c r="AN125" t="s" s="2">
         <v>82</v>
@@ -17291,10 +17311,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>598</v>
+        <v>606</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>598</v>
+        <v>606</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17320,13 +17340,13 @@
         <v>121</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>599</v>
+        <v>607</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>600</v>
+        <v>608</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>601</v>
+        <v>609</v>
       </c>
       <c r="O126" s="2"/>
       <c r="P126" t="s" s="2">
@@ -17376,7 +17396,7 @@
         <v>82</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>598</v>
+        <v>606</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>79</v>
@@ -17385,7 +17405,7 @@
         <v>92</v>
       </c>
       <c r="AI126" t="s" s="2">
-        <v>602</v>
+        <v>610</v>
       </c>
       <c r="AJ126" t="s" s="2">
         <v>103</v>
@@ -17394,10 +17414,10 @@
         <v>82</v>
       </c>
       <c r="AL126" t="s" s="2">
-        <v>603</v>
+        <v>611</v>
       </c>
       <c r="AM126" t="s" s="2">
-        <v>603</v>
+        <v>611</v>
       </c>
       <c r="AN126" t="s" s="2">
         <v>82</v>
@@ -17408,10 +17428,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>604</v>
+        <v>612</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>604</v>
+        <v>612</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17437,16 +17457,16 @@
         <v>111</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>605</v>
+        <v>613</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>606</v>
+        <v>614</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>607</v>
+        <v>615</v>
       </c>
       <c r="O127" t="s" s="2">
-        <v>608</v>
+        <v>616</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>82</v>
@@ -17474,10 +17494,10 @@
         <v>163</v>
       </c>
       <c r="Y127" t="s" s="2">
-        <v>609</v>
+        <v>617</v>
       </c>
       <c r="Z127" t="s" s="2">
-        <v>610</v>
+        <v>618</v>
       </c>
       <c r="AA127" t="s" s="2">
         <v>82</v>
@@ -17495,7 +17515,7 @@
         <v>82</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>604</v>
+        <v>612</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>79</v>
@@ -17513,7 +17533,7 @@
         <v>82</v>
       </c>
       <c r="AL127" t="s" s="2">
-        <v>611</v>
+        <v>619</v>
       </c>
       <c r="AM127" t="s" s="2">
         <v>168</v>
@@ -17527,10 +17547,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>612</v>
+        <v>620</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>612</v>
+        <v>620</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17556,16 +17576,16 @@
         <v>172</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>613</v>
+        <v>621</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>614</v>
+        <v>622</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>615</v>
+        <v>623</v>
       </c>
       <c r="O128" t="s" s="2">
-        <v>616</v>
+        <v>624</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>82</v>
@@ -17593,10 +17613,10 @@
         <v>115</v>
       </c>
       <c r="Y128" t="s" s="2">
-        <v>617</v>
+        <v>625</v>
       </c>
       <c r="Z128" t="s" s="2">
-        <v>618</v>
+        <v>626</v>
       </c>
       <c r="AA128" t="s" s="2">
         <v>82</v>
@@ -17614,7 +17634,7 @@
         <v>82</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>612</v>
+        <v>620</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>79</v>
@@ -17632,7 +17652,7 @@
         <v>82</v>
       </c>
       <c r="AL128" t="s" s="2">
-        <v>619</v>
+        <v>627</v>
       </c>
       <c r="AM128" t="s" s="2">
         <v>168</v>
@@ -17646,10 +17666,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>620</v>
+        <v>628</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>620</v>
+        <v>628</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17672,16 +17692,16 @@
         <v>82</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>562</v>
+        <v>570</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>621</v>
+        <v>629</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>622</v>
+        <v>630</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>623</v>
+        <v>631</v>
       </c>
       <c r="O129" s="2"/>
       <c r="P129" t="s" s="2">
@@ -17731,7 +17751,7 @@
         <v>82</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>620</v>
+        <v>628</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>79</v>
@@ -17740,7 +17760,7 @@
         <v>80</v>
       </c>
       <c r="AI129" t="s" s="2">
-        <v>624</v>
+        <v>632</v>
       </c>
       <c r="AJ129" t="s" s="2">
         <v>103</v>
@@ -17749,10 +17769,10 @@
         <v>82</v>
       </c>
       <c r="AL129" t="s" s="2">
-        <v>625</v>
+        <v>633</v>
       </c>
       <c r="AM129" t="s" s="2">
-        <v>626</v>
+        <v>634</v>
       </c>
       <c r="AN129" t="s" s="2">
         <v>82</v>
@@ -17763,10 +17783,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>627</v>
+        <v>635</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>627</v>
+        <v>635</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17792,16 +17812,16 @@
         <v>172</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>628</v>
+        <v>636</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>629</v>
+        <v>637</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>630</v>
+        <v>638</v>
       </c>
       <c r="O130" t="s" s="2">
-        <v>631</v>
+        <v>639</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>82</v>
@@ -17829,37 +17849,37 @@
         <v>115</v>
       </c>
       <c r="Y130" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="Z130" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="AA130" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB130" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC130" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD130" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE130" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF130" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="AG130" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH130" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI130" t="s" s="2">
         <v>632</v>
-      </c>
-      <c r="Z130" t="s" s="2">
-        <v>633</v>
-      </c>
-      <c r="AA130" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB130" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC130" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD130" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE130" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF130" t="s" s="2">
-        <v>627</v>
-      </c>
-      <c r="AG130" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH130" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI130" t="s" s="2">
-        <v>624</v>
       </c>
       <c r="AJ130" t="s" s="2">
         <v>103</v>
@@ -17868,7 +17888,7 @@
         <v>82</v>
       </c>
       <c r="AL130" t="s" s="2">
-        <v>634</v>
+        <v>642</v>
       </c>
       <c r="AM130" t="s" s="2">
         <v>168</v>
@@ -17882,10 +17902,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>635</v>
+        <v>643</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>635</v>
+        <v>643</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17911,13 +17931,13 @@
         <v>83</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>636</v>
+        <v>644</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>637</v>
+        <v>645</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>638</v>
+        <v>646</v>
       </c>
       <c r="O131" s="2"/>
       <c r="P131" t="s" s="2">
@@ -17967,7 +17987,7 @@
         <v>82</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>635</v>
+        <v>643</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>79</v>
@@ -17976,7 +17996,7 @@
         <v>80</v>
       </c>
       <c r="AI131" t="s" s="2">
-        <v>602</v>
+        <v>610</v>
       </c>
       <c r="AJ131" t="s" s="2">
         <v>103</v>
@@ -17985,10 +18005,10 @@
         <v>82</v>
       </c>
       <c r="AL131" t="s" s="2">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="AM131" t="s" s="2">
-        <v>639</v>
+        <v>647</v>
       </c>
       <c r="AN131" t="s" s="2">
         <v>82</v>
@@ -17999,13 +18019,13 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>640</v>
+        <v>648</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>566</v>
+        <v>574</v>
       </c>
       <c r="C132" t="s" s="2">
-        <v>641</v>
+        <v>649</v>
       </c>
       <c r="D132" t="s" s="2">
         <v>82</v>
@@ -18027,13 +18047,13 @@
         <v>82</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>642</v>
+        <v>650</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>643</v>
+        <v>651</v>
       </c>
       <c r="N132" s="2"/>
       <c r="O132" s="2"/>
@@ -18084,7 +18104,7 @@
         <v>82</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>566</v>
+        <v>574</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>79</v>
@@ -18096,16 +18116,16 @@
         <v>82</v>
       </c>
       <c r="AJ132" t="s" s="2">
-        <v>570</v>
+        <v>578</v>
       </c>
       <c r="AK132" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL132" t="s" s="2">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="AM132" t="s" s="2">
-        <v>572</v>
+        <v>580</v>
       </c>
       <c r="AN132" t="s" s="2">
         <v>82</v>
@@ -18116,10 +18136,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>644</v>
+        <v>652</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>573</v>
+        <v>581</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18231,10 +18251,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>645</v>
+        <v>653</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18348,14 +18368,14 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>646</v>
+        <v>654</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>575</v>
+        <v>583</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E135" s="2"/>
       <c r="F135" t="s" s="2">
@@ -18377,10 +18397,10 @@
         <v>137</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>470</v>
+        <v>478</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>471</v>
+        <v>479</v>
       </c>
       <c r="N135" t="s" s="2">
         <v>140</v>
@@ -18435,7 +18455,7 @@
         <v>82</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>472</v>
+        <v>480</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>79</v>
@@ -18467,14 +18487,14 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>647</v>
+        <v>655</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>576</v>
+        <v>584</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
-        <v>577</v>
+        <v>585</v>
       </c>
       <c r="E136" s="2"/>
       <c r="F136" t="s" s="2">
@@ -18496,16 +18516,16 @@
         <v>184</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>578</v>
+        <v>586</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>579</v>
+        <v>587</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>580</v>
+        <v>588</v>
       </c>
       <c r="O136" t="s" s="2">
-        <v>581</v>
+        <v>589</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>82</v>
@@ -18554,7 +18574,7 @@
         <v>82</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>576</v>
+        <v>584</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>79</v>
@@ -18572,10 +18592,10 @@
         <v>82</v>
       </c>
       <c r="AL136" t="s" s="2">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="AM136" t="s" s="2">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="AN136" t="s" s="2">
         <v>82</v>
@@ -18586,10 +18606,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>648</v>
+        <v>656</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>582</v>
+        <v>590</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -18615,16 +18635,16 @@
         <v>172</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>583</v>
+        <v>591</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>584</v>
+        <v>592</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="O137" t="s" s="2">
-        <v>586</v>
+        <v>594</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>82</v>
@@ -18649,13 +18669,13 @@
         <v>82</v>
       </c>
       <c r="X137" t="s" s="2">
-        <v>553</v>
+        <v>561</v>
       </c>
       <c r="Y137" t="s" s="2">
-        <v>587</v>
+        <v>595</v>
       </c>
       <c r="Z137" t="s" s="2">
-        <v>588</v>
+        <v>596</v>
       </c>
       <c r="AA137" t="s" s="2">
         <v>82</v>
@@ -18673,7 +18693,7 @@
         <v>82</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>582</v>
+        <v>590</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>79</v>
@@ -18705,10 +18725,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>649</v>
+        <v>657</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>589</v>
+        <v>597</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -18731,17 +18751,17 @@
         <v>82</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>590</v>
+        <v>598</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>591</v>
+        <v>599</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>592</v>
+        <v>600</v>
       </c>
       <c r="N138" s="2"/>
       <c r="O138" t="s" s="2">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="P138" t="s" s="2">
         <v>82</v>
@@ -18790,7 +18810,7 @@
         <v>82</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>589</v>
+        <v>597</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>79</v>
@@ -18808,24 +18828,24 @@
         <v>82</v>
       </c>
       <c r="AL138" t="s" s="2">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="AM138" t="s" s="2">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="AN138" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO138" t="s" s="2">
-        <v>427</v>
+        <v>435</v>
       </c>
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>650</v>
+        <v>658</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>593</v>
+        <v>601</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -18848,16 +18868,16 @@
         <v>82</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>562</v>
+        <v>570</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>594</v>
+        <v>602</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>595</v>
+        <v>603</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>596</v>
+        <v>604</v>
       </c>
       <c r="O139" s="2"/>
       <c r="P139" t="s" s="2">
@@ -18907,7 +18927,7 @@
         <v>82</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>593</v>
+        <v>601</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>79</v>
@@ -18928,7 +18948,7 @@
         <v>82</v>
       </c>
       <c r="AM139" t="s" s="2">
-        <v>597</v>
+        <v>605</v>
       </c>
       <c r="AN139" t="s" s="2">
         <v>82</v>
@@ -18939,10 +18959,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>651</v>
+        <v>659</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>598</v>
+        <v>606</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -18968,13 +18988,13 @@
         <v>121</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>599</v>
+        <v>607</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>600</v>
+        <v>608</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>601</v>
+        <v>609</v>
       </c>
       <c r="O140" s="2"/>
       <c r="P140" t="s" s="2">
@@ -19024,7 +19044,7 @@
         <v>82</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>598</v>
+        <v>606</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>79</v>
@@ -19033,7 +19053,7 @@
         <v>92</v>
       </c>
       <c r="AI140" t="s" s="2">
-        <v>602</v>
+        <v>610</v>
       </c>
       <c r="AJ140" t="s" s="2">
         <v>103</v>
@@ -19042,10 +19062,10 @@
         <v>82</v>
       </c>
       <c r="AL140" t="s" s="2">
-        <v>603</v>
+        <v>611</v>
       </c>
       <c r="AM140" t="s" s="2">
-        <v>603</v>
+        <v>611</v>
       </c>
       <c r="AN140" t="s" s="2">
         <v>82</v>
@@ -19056,10 +19076,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>652</v>
+        <v>660</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>604</v>
+        <v>612</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19085,16 +19105,16 @@
         <v>111</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>605</v>
+        <v>613</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>606</v>
+        <v>614</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>607</v>
+        <v>615</v>
       </c>
       <c r="O141" t="s" s="2">
-        <v>608</v>
+        <v>616</v>
       </c>
       <c r="P141" t="s" s="2">
         <v>82</v>
@@ -19122,10 +19142,10 @@
         <v>163</v>
       </c>
       <c r="Y141" t="s" s="2">
-        <v>609</v>
+        <v>617</v>
       </c>
       <c r="Z141" t="s" s="2">
-        <v>610</v>
+        <v>618</v>
       </c>
       <c r="AA141" t="s" s="2">
         <v>82</v>
@@ -19143,7 +19163,7 @@
         <v>82</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>604</v>
+        <v>612</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>79</v>
@@ -19161,7 +19181,7 @@
         <v>82</v>
       </c>
       <c r="AL141" t="s" s="2">
-        <v>611</v>
+        <v>619</v>
       </c>
       <c r="AM141" t="s" s="2">
         <v>168</v>
@@ -19175,10 +19195,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>653</v>
+        <v>661</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>612</v>
+        <v>620</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19204,16 +19224,16 @@
         <v>172</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>613</v>
+        <v>621</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>614</v>
+        <v>622</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>615</v>
+        <v>623</v>
       </c>
       <c r="O142" t="s" s="2">
-        <v>616</v>
+        <v>624</v>
       </c>
       <c r="P142" t="s" s="2">
         <v>82</v>
@@ -19241,10 +19261,10 @@
         <v>115</v>
       </c>
       <c r="Y142" t="s" s="2">
-        <v>617</v>
+        <v>625</v>
       </c>
       <c r="Z142" t="s" s="2">
-        <v>618</v>
+        <v>626</v>
       </c>
       <c r="AA142" t="s" s="2">
         <v>82</v>
@@ -19262,7 +19282,7 @@
         <v>82</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>612</v>
+        <v>620</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>79</v>
@@ -19280,7 +19300,7 @@
         <v>82</v>
       </c>
       <c r="AL142" t="s" s="2">
-        <v>619</v>
+        <v>627</v>
       </c>
       <c r="AM142" t="s" s="2">
         <v>168</v>
@@ -19294,10 +19314,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>654</v>
+        <v>662</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>620</v>
+        <v>628</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19320,16 +19340,16 @@
         <v>82</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>655</v>
+        <v>663</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>621</v>
+        <v>629</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>622</v>
+        <v>630</v>
       </c>
       <c r="N143" t="s" s="2">
-        <v>623</v>
+        <v>631</v>
       </c>
       <c r="O143" s="2"/>
       <c r="P143" t="s" s="2">
@@ -19379,7 +19399,7 @@
         <v>82</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>620</v>
+        <v>628</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>79</v>
@@ -19388,7 +19408,7 @@
         <v>80</v>
       </c>
       <c r="AI143" t="s" s="2">
-        <v>624</v>
+        <v>632</v>
       </c>
       <c r="AJ143" t="s" s="2">
         <v>103</v>
@@ -19397,10 +19417,10 @@
         <v>82</v>
       </c>
       <c r="AL143" t="s" s="2">
-        <v>625</v>
+        <v>633</v>
       </c>
       <c r="AM143" t="s" s="2">
-        <v>626</v>
+        <v>634</v>
       </c>
       <c r="AN143" t="s" s="2">
         <v>82</v>
@@ -19411,10 +19431,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>656</v>
+        <v>664</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>657</v>
+        <v>665</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -19526,10 +19546,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>658</v>
+        <v>666</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>659</v>
+        <v>667</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -19643,10 +19663,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>660</v>
+        <v>668</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>661</v>
+        <v>669</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -19672,13 +19692,13 @@
         <v>184</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="N146" t="s" s="2">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="O146" s="2"/>
       <c r="P146" t="s" s="2">
@@ -19728,7 +19748,7 @@
         <v>82</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>79</v>
@@ -19737,7 +19757,7 @@
         <v>92</v>
       </c>
       <c r="AI146" t="s" s="2">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="AJ146" t="s" s="2">
         <v>103</v>
@@ -19760,10 +19780,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>662</v>
+        <v>670</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>663</v>
+        <v>671</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -19789,13 +19809,13 @@
         <v>105</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="O147" s="2"/>
       <c r="P147" t="s" s="2">
@@ -19821,13 +19841,13 @@
         <v>82</v>
       </c>
       <c r="X147" t="s" s="2">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="Y147" t="s" s="2">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="Z147" t="s" s="2">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="AA147" t="s" s="2">
         <v>82</v>
@@ -19845,7 +19865,7 @@
         <v>82</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>79</v>
@@ -19877,10 +19897,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>664</v>
+        <v>672</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>665</v>
+        <v>673</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -19906,13 +19926,13 @@
         <v>149</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="O148" s="2"/>
       <c r="P148" t="s" s="2">
@@ -19962,7 +19982,7 @@
         <v>82</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>79</v>
@@ -19980,7 +20000,7 @@
         <v>82</v>
       </c>
       <c r="AL148" t="s" s="2">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="AM148" t="s" s="2">
         <v>82</v>
@@ -19994,10 +20014,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>666</v>
+        <v>674</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>667</v>
+        <v>675</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20023,13 +20043,13 @@
         <v>184</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="O149" s="2"/>
       <c r="P149" t="s" s="2">
@@ -20079,7 +20099,7 @@
         <v>82</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>79</v>
@@ -20111,10 +20131,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>668</v>
+        <v>676</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>627</v>
+        <v>635</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20140,16 +20160,16 @@
         <v>172</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>628</v>
+        <v>636</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>629</v>
+        <v>637</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>630</v>
+        <v>638</v>
       </c>
       <c r="O150" t="s" s="2">
-        <v>631</v>
+        <v>639</v>
       </c>
       <c r="P150" t="s" s="2">
         <v>82</v>
@@ -20177,37 +20197,37 @@
         <v>115</v>
       </c>
       <c r="Y150" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="Z150" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="AA150" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB150" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC150" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD150" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE150" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF150" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="AG150" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH150" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI150" t="s" s="2">
         <v>632</v>
-      </c>
-      <c r="Z150" t="s" s="2">
-        <v>633</v>
-      </c>
-      <c r="AA150" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB150" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC150" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD150" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE150" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF150" t="s" s="2">
-        <v>627</v>
-      </c>
-      <c r="AG150" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH150" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI150" t="s" s="2">
-        <v>624</v>
       </c>
       <c r="AJ150" t="s" s="2">
         <v>103</v>
@@ -20216,7 +20236,7 @@
         <v>82</v>
       </c>
       <c r="AL150" t="s" s="2">
-        <v>634</v>
+        <v>642</v>
       </c>
       <c r="AM150" t="s" s="2">
         <v>168</v>
@@ -20230,10 +20250,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>669</v>
+        <v>677</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>635</v>
+        <v>643</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20259,13 +20279,13 @@
         <v>82</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>636</v>
+        <v>644</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>637</v>
+        <v>645</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>638</v>
+        <v>646</v>
       </c>
       <c r="O151" s="2"/>
       <c r="P151" t="s" s="2">
@@ -20315,7 +20335,7 @@
         <v>82</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>635</v>
+        <v>643</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>79</v>
@@ -20324,7 +20344,7 @@
         <v>80</v>
       </c>
       <c r="AI151" t="s" s="2">
-        <v>602</v>
+        <v>610</v>
       </c>
       <c r="AJ151" t="s" s="2">
         <v>103</v>
@@ -20333,10 +20353,10 @@
         <v>82</v>
       </c>
       <c r="AL151" t="s" s="2">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="AM151" t="s" s="2">
-        <v>639</v>
+        <v>647</v>
       </c>
       <c r="AN151" t="s" s="2">
         <v>82</v>
@@ -20347,13 +20367,13 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>566</v>
+        <v>574</v>
       </c>
       <c r="C152" t="s" s="2">
-        <v>671</v>
+        <v>679</v>
       </c>
       <c r="D152" t="s" s="2">
         <v>82</v>
@@ -20375,13 +20395,13 @@
         <v>82</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>672</v>
+        <v>680</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>643</v>
+        <v>651</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" s="2"/>
@@ -20432,7 +20452,7 @@
         <v>82</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>566</v>
+        <v>574</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>79</v>
@@ -20444,16 +20464,16 @@
         <v>82</v>
       </c>
       <c r="AJ152" t="s" s="2">
-        <v>570</v>
+        <v>578</v>
       </c>
       <c r="AK152" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL152" t="s" s="2">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="AM152" t="s" s="2">
-        <v>572</v>
+        <v>580</v>
       </c>
       <c r="AN152" t="s" s="2">
         <v>82</v>
@@ -20464,10 +20484,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>673</v>
+        <v>681</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>573</v>
+        <v>581</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -20579,10 +20599,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>674</v>
+        <v>682</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -20696,14 +20716,14 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>675</v>
+        <v>683</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>575</v>
+        <v>583</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E155" s="2"/>
       <c r="F155" t="s" s="2">
@@ -20725,10 +20745,10 @@
         <v>137</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>470</v>
+        <v>478</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>471</v>
+        <v>479</v>
       </c>
       <c r="N155" t="s" s="2">
         <v>140</v>
@@ -20783,7 +20803,7 @@
         <v>82</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>472</v>
+        <v>480</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>79</v>
@@ -20815,14 +20835,14 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>676</v>
+        <v>684</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>576</v>
+        <v>584</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
-        <v>577</v>
+        <v>585</v>
       </c>
       <c r="E156" s="2"/>
       <c r="F156" t="s" s="2">
@@ -20844,16 +20864,16 @@
         <v>184</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>578</v>
+        <v>586</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>579</v>
+        <v>587</v>
       </c>
       <c r="N156" t="s" s="2">
-        <v>580</v>
+        <v>588</v>
       </c>
       <c r="O156" t="s" s="2">
-        <v>581</v>
+        <v>589</v>
       </c>
       <c r="P156" t="s" s="2">
         <v>82</v>
@@ -20902,7 +20922,7 @@
         <v>82</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>576</v>
+        <v>584</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>79</v>
@@ -20920,10 +20940,10 @@
         <v>82</v>
       </c>
       <c r="AL156" t="s" s="2">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="AM156" t="s" s="2">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="AN156" t="s" s="2">
         <v>82</v>
@@ -20934,10 +20954,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>677</v>
+        <v>685</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>582</v>
+        <v>590</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -20963,16 +20983,16 @@
         <v>172</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>583</v>
+        <v>591</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>584</v>
+        <v>592</v>
       </c>
       <c r="N157" t="s" s="2">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="O157" t="s" s="2">
-        <v>586</v>
+        <v>594</v>
       </c>
       <c r="P157" t="s" s="2">
         <v>82</v>
@@ -20997,13 +21017,13 @@
         <v>82</v>
       </c>
       <c r="X157" t="s" s="2">
-        <v>553</v>
+        <v>561</v>
       </c>
       <c r="Y157" t="s" s="2">
-        <v>587</v>
+        <v>595</v>
       </c>
       <c r="Z157" t="s" s="2">
-        <v>588</v>
+        <v>596</v>
       </c>
       <c r="AA157" t="s" s="2">
         <v>82</v>
@@ -21021,7 +21041,7 @@
         <v>82</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>582</v>
+        <v>590</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>79</v>
@@ -21053,10 +21073,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>678</v>
+        <v>686</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>589</v>
+        <v>597</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21079,17 +21099,17 @@
         <v>82</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>590</v>
+        <v>598</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>591</v>
+        <v>599</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>592</v>
+        <v>600</v>
       </c>
       <c r="N158" s="2"/>
       <c r="O158" t="s" s="2">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="P158" t="s" s="2">
         <v>82</v>
@@ -21138,7 +21158,7 @@
         <v>82</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>589</v>
+        <v>597</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>79</v>
@@ -21156,24 +21176,24 @@
         <v>82</v>
       </c>
       <c r="AL158" t="s" s="2">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="AM158" t="s" s="2">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="AN158" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO158" t="s" s="2">
-        <v>427</v>
+        <v>435</v>
       </c>
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>679</v>
+        <v>687</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>593</v>
+        <v>601</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21196,16 +21216,16 @@
         <v>82</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>562</v>
+        <v>570</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>594</v>
+        <v>602</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>595</v>
+        <v>603</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>596</v>
+        <v>604</v>
       </c>
       <c r="O159" s="2"/>
       <c r="P159" t="s" s="2">
@@ -21255,7 +21275,7 @@
         <v>82</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>593</v>
+        <v>601</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>79</v>
@@ -21276,7 +21296,7 @@
         <v>82</v>
       </c>
       <c r="AM159" t="s" s="2">
-        <v>597</v>
+        <v>605</v>
       </c>
       <c r="AN159" t="s" s="2">
         <v>82</v>
@@ -21287,10 +21307,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>680</v>
+        <v>688</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>598</v>
+        <v>606</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -21316,13 +21336,13 @@
         <v>121</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>599</v>
+        <v>607</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>600</v>
+        <v>608</v>
       </c>
       <c r="N160" t="s" s="2">
-        <v>601</v>
+        <v>609</v>
       </c>
       <c r="O160" s="2"/>
       <c r="P160" t="s" s="2">
@@ -21372,7 +21392,7 @@
         <v>82</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>598</v>
+        <v>606</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>79</v>
@@ -21381,7 +21401,7 @@
         <v>92</v>
       </c>
       <c r="AI160" t="s" s="2">
-        <v>602</v>
+        <v>610</v>
       </c>
       <c r="AJ160" t="s" s="2">
         <v>103</v>
@@ -21390,10 +21410,10 @@
         <v>82</v>
       </c>
       <c r="AL160" t="s" s="2">
-        <v>603</v>
+        <v>611</v>
       </c>
       <c r="AM160" t="s" s="2">
-        <v>603</v>
+        <v>611</v>
       </c>
       <c r="AN160" t="s" s="2">
         <v>82</v>
@@ -21404,10 +21424,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>681</v>
+        <v>689</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>604</v>
+        <v>612</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -21433,16 +21453,16 @@
         <v>111</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>605</v>
+        <v>613</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>606</v>
+        <v>614</v>
       </c>
       <c r="N161" t="s" s="2">
-        <v>607</v>
+        <v>615</v>
       </c>
       <c r="O161" t="s" s="2">
-        <v>608</v>
+        <v>616</v>
       </c>
       <c r="P161" t="s" s="2">
         <v>82</v>
@@ -21470,10 +21490,10 @@
         <v>163</v>
       </c>
       <c r="Y161" t="s" s="2">
-        <v>609</v>
+        <v>617</v>
       </c>
       <c r="Z161" t="s" s="2">
-        <v>610</v>
+        <v>618</v>
       </c>
       <c r="AA161" t="s" s="2">
         <v>82</v>
@@ -21491,7 +21511,7 @@
         <v>82</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>604</v>
+        <v>612</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>79</v>
@@ -21509,7 +21529,7 @@
         <v>82</v>
       </c>
       <c r="AL161" t="s" s="2">
-        <v>611</v>
+        <v>619</v>
       </c>
       <c r="AM161" t="s" s="2">
         <v>168</v>
@@ -21523,10 +21543,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>682</v>
+        <v>690</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>612</v>
+        <v>620</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -21552,16 +21572,16 @@
         <v>172</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>613</v>
+        <v>621</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>614</v>
+        <v>622</v>
       </c>
       <c r="N162" t="s" s="2">
-        <v>615</v>
+        <v>623</v>
       </c>
       <c r="O162" t="s" s="2">
-        <v>616</v>
+        <v>624</v>
       </c>
       <c r="P162" t="s" s="2">
         <v>82</v>
@@ -21589,10 +21609,10 @@
         <v>115</v>
       </c>
       <c r="Y162" t="s" s="2">
-        <v>617</v>
+        <v>625</v>
       </c>
       <c r="Z162" t="s" s="2">
-        <v>618</v>
+        <v>626</v>
       </c>
       <c r="AA162" t="s" s="2">
         <v>82</v>
@@ -21610,7 +21630,7 @@
         <v>82</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>612</v>
+        <v>620</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>79</v>
@@ -21628,7 +21648,7 @@
         <v>82</v>
       </c>
       <c r="AL162" t="s" s="2">
-        <v>619</v>
+        <v>627</v>
       </c>
       <c r="AM162" t="s" s="2">
         <v>168</v>
@@ -21642,10 +21662,10 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>683</v>
+        <v>691</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>620</v>
+        <v>628</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -21668,16 +21688,16 @@
         <v>82</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>684</v>
+        <v>692</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>621</v>
+        <v>629</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>622</v>
+        <v>630</v>
       </c>
       <c r="N163" t="s" s="2">
-        <v>623</v>
+        <v>631</v>
       </c>
       <c r="O163" s="2"/>
       <c r="P163" t="s" s="2">
@@ -21727,7 +21747,7 @@
         <v>82</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>620</v>
+        <v>628</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>79</v>
@@ -21736,7 +21756,7 @@
         <v>80</v>
       </c>
       <c r="AI163" t="s" s="2">
-        <v>624</v>
+        <v>632</v>
       </c>
       <c r="AJ163" t="s" s="2">
         <v>103</v>
@@ -21745,10 +21765,10 @@
         <v>82</v>
       </c>
       <c r="AL163" t="s" s="2">
-        <v>625</v>
+        <v>633</v>
       </c>
       <c r="AM163" t="s" s="2">
-        <v>626</v>
+        <v>634</v>
       </c>
       <c r="AN163" t="s" s="2">
         <v>82</v>
@@ -21759,10 +21779,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>685</v>
+        <v>693</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>657</v>
+        <v>665</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -21874,10 +21894,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>686</v>
+        <v>694</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>659</v>
+        <v>667</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -21991,10 +22011,10 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>687</v>
+        <v>695</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>661</v>
+        <v>669</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22020,13 +22040,13 @@
         <v>184</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="N166" t="s" s="2">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="O166" s="2"/>
       <c r="P166" t="s" s="2">
@@ -22076,7 +22096,7 @@
         <v>82</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>79</v>
@@ -22085,7 +22105,7 @@
         <v>92</v>
       </c>
       <c r="AI166" t="s" s="2">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="AJ166" t="s" s="2">
         <v>103</v>
@@ -22108,10 +22128,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>688</v>
+        <v>696</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>663</v>
+        <v>671</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -22137,13 +22157,13 @@
         <v>105</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="N167" t="s" s="2">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="O167" s="2"/>
       <c r="P167" t="s" s="2">
@@ -22169,13 +22189,13 @@
         <v>82</v>
       </c>
       <c r="X167" t="s" s="2">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="Y167" t="s" s="2">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="Z167" t="s" s="2">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="AA167" t="s" s="2">
         <v>82</v>
@@ -22193,7 +22213,7 @@
         <v>82</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>79</v>
@@ -22225,10 +22245,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>689</v>
+        <v>697</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>665</v>
+        <v>673</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -22254,13 +22274,13 @@
         <v>149</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="N168" t="s" s="2">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="O168" s="2"/>
       <c r="P168" t="s" s="2">
@@ -22310,7 +22330,7 @@
         <v>82</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>79</v>
@@ -22328,7 +22348,7 @@
         <v>82</v>
       </c>
       <c r="AL168" t="s" s="2">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="AM168" t="s" s="2">
         <v>82</v>
@@ -22342,10 +22362,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>690</v>
+        <v>698</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>667</v>
+        <v>675</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -22371,13 +22391,13 @@
         <v>184</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="N169" t="s" s="2">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="O169" s="2"/>
       <c r="P169" t="s" s="2">
@@ -22427,7 +22447,7 @@
         <v>82</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>79</v>
@@ -22459,10 +22479,10 @@
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>691</v>
+        <v>699</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>627</v>
+        <v>635</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -22488,16 +22508,16 @@
         <v>172</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>692</v>
+        <v>700</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>629</v>
+        <v>637</v>
       </c>
       <c r="N170" t="s" s="2">
-        <v>630</v>
+        <v>638</v>
       </c>
       <c r="O170" t="s" s="2">
-        <v>631</v>
+        <v>639</v>
       </c>
       <c r="P170" t="s" s="2">
         <v>82</v>
@@ -22525,37 +22545,37 @@
         <v>115</v>
       </c>
       <c r="Y170" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="Z170" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="AA170" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB170" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC170" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD170" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE170" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF170" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="AG170" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH170" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI170" t="s" s="2">
         <v>632</v>
-      </c>
-      <c r="Z170" t="s" s="2">
-        <v>633</v>
-      </c>
-      <c r="AA170" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB170" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC170" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD170" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE170" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF170" t="s" s="2">
-        <v>627</v>
-      </c>
-      <c r="AG170" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH170" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI170" t="s" s="2">
-        <v>624</v>
       </c>
       <c r="AJ170" t="s" s="2">
         <v>103</v>
@@ -22564,7 +22584,7 @@
         <v>82</v>
       </c>
       <c r="AL170" t="s" s="2">
-        <v>634</v>
+        <v>642</v>
       </c>
       <c r="AM170" t="s" s="2">
         <v>168</v>
@@ -22578,10 +22598,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>693</v>
+        <v>701</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>694</v>
+        <v>702</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -22693,10 +22713,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>695</v>
+        <v>703</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>696</v>
+        <v>704</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -22810,10 +22830,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>697</v>
+        <v>705</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>698</v>
+        <v>706</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -22929,10 +22949,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>699</v>
+        <v>707</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>700</v>
+        <v>708</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23044,10 +23064,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>702</v>
+        <v>710</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -23161,10 +23181,10 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>703</v>
+        <v>711</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -23280,10 +23300,10 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>705</v>
+        <v>713</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>706</v>
+        <v>714</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -23397,10 +23417,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>707</v>
+        <v>715</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>708</v>
+        <v>716</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -23514,10 +23534,10 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>709</v>
+        <v>717</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>710</v>
+        <v>718</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -23631,10 +23651,10 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>711</v>
+        <v>719</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>712</v>
+        <v>720</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -23750,10 +23770,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>713</v>
+        <v>721</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>714</v>
+        <v>722</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -23869,10 +23889,10 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>715</v>
+        <v>723</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>635</v>
+        <v>643</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -23898,13 +23918,13 @@
         <v>82</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>636</v>
+        <v>644</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>637</v>
+        <v>645</v>
       </c>
       <c r="N182" t="s" s="2">
-        <v>638</v>
+        <v>646</v>
       </c>
       <c r="O182" s="2"/>
       <c r="P182" t="s" s="2">
@@ -23954,7 +23974,7 @@
         <v>82</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>635</v>
+        <v>643</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>79</v>
@@ -23963,7 +23983,7 @@
         <v>80</v>
       </c>
       <c r="AI182" t="s" s="2">
-        <v>602</v>
+        <v>610</v>
       </c>
       <c r="AJ182" t="s" s="2">
         <v>103</v>
@@ -23972,10 +23992,10 @@
         <v>82</v>
       </c>
       <c r="AL182" t="s" s="2">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="AM182" t="s" s="2">
-        <v>639</v>
+        <v>647</v>
       </c>
       <c r="AN182" t="s" s="2">
         <v>82</v>
@@ -23986,13 +24006,13 @@
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>716</v>
+        <v>724</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>566</v>
+        <v>574</v>
       </c>
       <c r="C183" t="s" s="2">
-        <v>717</v>
+        <v>725</v>
       </c>
       <c r="D183" t="s" s="2">
         <v>82</v>
@@ -24014,13 +24034,13 @@
         <v>82</v>
       </c>
       <c r="K183" t="s" s="2">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>718</v>
+        <v>726</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>643</v>
+        <v>651</v>
       </c>
       <c r="N183" s="2"/>
       <c r="O183" s="2"/>
@@ -24071,7 +24091,7 @@
         <v>82</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>566</v>
+        <v>574</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>79</v>
@@ -24083,16 +24103,16 @@
         <v>82</v>
       </c>
       <c r="AJ183" t="s" s="2">
-        <v>570</v>
+        <v>578</v>
       </c>
       <c r="AK183" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL183" t="s" s="2">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="AM183" t="s" s="2">
-        <v>572</v>
+        <v>580</v>
       </c>
       <c r="AN183" t="s" s="2">
         <v>82</v>
@@ -24103,10 +24123,10 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>719</v>
+        <v>727</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>573</v>
+        <v>581</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -24218,10 +24238,10 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>720</v>
+        <v>728</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -24335,14 +24355,14 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>721</v>
+        <v>729</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>575</v>
+        <v>583</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E186" s="2"/>
       <c r="F186" t="s" s="2">
@@ -24364,10 +24384,10 @@
         <v>137</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>470</v>
+        <v>478</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>471</v>
+        <v>479</v>
       </c>
       <c r="N186" t="s" s="2">
         <v>140</v>
@@ -24422,7 +24442,7 @@
         <v>82</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>472</v>
+        <v>480</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>79</v>
@@ -24454,14 +24474,14 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>576</v>
+        <v>584</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
-        <v>577</v>
+        <v>585</v>
       </c>
       <c r="E187" s="2"/>
       <c r="F187" t="s" s="2">
@@ -24483,16 +24503,16 @@
         <v>184</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>578</v>
+        <v>586</v>
       </c>
       <c r="M187" t="s" s="2">
-        <v>579</v>
+        <v>587</v>
       </c>
       <c r="N187" t="s" s="2">
-        <v>580</v>
+        <v>588</v>
       </c>
       <c r="O187" t="s" s="2">
-        <v>581</v>
+        <v>589</v>
       </c>
       <c r="P187" t="s" s="2">
         <v>82</v>
@@ -24541,7 +24561,7 @@
         <v>82</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>576</v>
+        <v>584</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>79</v>
@@ -24559,10 +24579,10 @@
         <v>82</v>
       </c>
       <c r="AL187" t="s" s="2">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="AM187" t="s" s="2">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="AN187" t="s" s="2">
         <v>82</v>
@@ -24573,10 +24593,10 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>582</v>
+        <v>590</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -24602,16 +24622,16 @@
         <v>172</v>
       </c>
       <c r="L188" t="s" s="2">
-        <v>583</v>
+        <v>591</v>
       </c>
       <c r="M188" t="s" s="2">
-        <v>584</v>
+        <v>592</v>
       </c>
       <c r="N188" t="s" s="2">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="O188" t="s" s="2">
-        <v>586</v>
+        <v>594</v>
       </c>
       <c r="P188" t="s" s="2">
         <v>82</v>
@@ -24636,13 +24656,13 @@
         <v>82</v>
       </c>
       <c r="X188" t="s" s="2">
-        <v>553</v>
+        <v>561</v>
       </c>
       <c r="Y188" t="s" s="2">
-        <v>587</v>
+        <v>595</v>
       </c>
       <c r="Z188" t="s" s="2">
-        <v>588</v>
+        <v>596</v>
       </c>
       <c r="AA188" t="s" s="2">
         <v>82</v>
@@ -24660,7 +24680,7 @@
         <v>82</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>582</v>
+        <v>590</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>79</v>
@@ -24692,10 +24712,10 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>589</v>
+        <v>597</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -24718,17 +24738,17 @@
         <v>82</v>
       </c>
       <c r="K189" t="s" s="2">
-        <v>590</v>
+        <v>598</v>
       </c>
       <c r="L189" t="s" s="2">
-        <v>591</v>
+        <v>599</v>
       </c>
       <c r="M189" t="s" s="2">
-        <v>592</v>
+        <v>600</v>
       </c>
       <c r="N189" s="2"/>
       <c r="O189" t="s" s="2">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="P189" t="s" s="2">
         <v>82</v>
@@ -24777,7 +24797,7 @@
         <v>82</v>
       </c>
       <c r="AF189" t="s" s="2">
-        <v>589</v>
+        <v>597</v>
       </c>
       <c r="AG189" t="s" s="2">
         <v>79</v>
@@ -24795,24 +24815,24 @@
         <v>82</v>
       </c>
       <c r="AL189" t="s" s="2">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="AM189" t="s" s="2">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="AN189" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO189" t="s" s="2">
-        <v>427</v>
+        <v>435</v>
       </c>
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>725</v>
+        <v>733</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>593</v>
+        <v>601</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -24835,16 +24855,16 @@
         <v>82</v>
       </c>
       <c r="K190" t="s" s="2">
-        <v>562</v>
+        <v>570</v>
       </c>
       <c r="L190" t="s" s="2">
-        <v>594</v>
+        <v>602</v>
       </c>
       <c r="M190" t="s" s="2">
-        <v>595</v>
+        <v>603</v>
       </c>
       <c r="N190" t="s" s="2">
-        <v>596</v>
+        <v>604</v>
       </c>
       <c r="O190" s="2"/>
       <c r="P190" t="s" s="2">
@@ -24894,7 +24914,7 @@
         <v>82</v>
       </c>
       <c r="AF190" t="s" s="2">
-        <v>593</v>
+        <v>601</v>
       </c>
       <c r="AG190" t="s" s="2">
         <v>79</v>
@@ -24915,7 +24935,7 @@
         <v>82</v>
       </c>
       <c r="AM190" t="s" s="2">
-        <v>597</v>
+        <v>605</v>
       </c>
       <c r="AN190" t="s" s="2">
         <v>82</v>
@@ -24926,10 +24946,10 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>726</v>
+        <v>734</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>598</v>
+        <v>606</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -24955,13 +24975,13 @@
         <v>121</v>
       </c>
       <c r="L191" t="s" s="2">
-        <v>599</v>
+        <v>607</v>
       </c>
       <c r="M191" t="s" s="2">
-        <v>600</v>
+        <v>608</v>
       </c>
       <c r="N191" t="s" s="2">
-        <v>601</v>
+        <v>609</v>
       </c>
       <c r="O191" s="2"/>
       <c r="P191" t="s" s="2">
@@ -25011,7 +25031,7 @@
         <v>82</v>
       </c>
       <c r="AF191" t="s" s="2">
-        <v>598</v>
+        <v>606</v>
       </c>
       <c r="AG191" t="s" s="2">
         <v>79</v>
@@ -25020,7 +25040,7 @@
         <v>92</v>
       </c>
       <c r="AI191" t="s" s="2">
-        <v>602</v>
+        <v>610</v>
       </c>
       <c r="AJ191" t="s" s="2">
         <v>103</v>
@@ -25029,10 +25049,10 @@
         <v>82</v>
       </c>
       <c r="AL191" t="s" s="2">
-        <v>603</v>
+        <v>611</v>
       </c>
       <c r="AM191" t="s" s="2">
-        <v>603</v>
+        <v>611</v>
       </c>
       <c r="AN191" t="s" s="2">
         <v>82</v>
@@ -25043,10 +25063,10 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>727</v>
+        <v>735</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>604</v>
+        <v>612</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -25072,16 +25092,16 @@
         <v>111</v>
       </c>
       <c r="L192" t="s" s="2">
-        <v>605</v>
+        <v>613</v>
       </c>
       <c r="M192" t="s" s="2">
-        <v>606</v>
+        <v>614</v>
       </c>
       <c r="N192" t="s" s="2">
-        <v>607</v>
+        <v>615</v>
       </c>
       <c r="O192" t="s" s="2">
-        <v>608</v>
+        <v>616</v>
       </c>
       <c r="P192" t="s" s="2">
         <v>82</v>
@@ -25109,10 +25129,10 @@
         <v>163</v>
       </c>
       <c r="Y192" t="s" s="2">
-        <v>609</v>
+        <v>617</v>
       </c>
       <c r="Z192" t="s" s="2">
-        <v>610</v>
+        <v>618</v>
       </c>
       <c r="AA192" t="s" s="2">
         <v>82</v>
@@ -25130,7 +25150,7 @@
         <v>82</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>604</v>
+        <v>612</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>79</v>
@@ -25148,7 +25168,7 @@
         <v>82</v>
       </c>
       <c r="AL192" t="s" s="2">
-        <v>611</v>
+        <v>619</v>
       </c>
       <c r="AM192" t="s" s="2">
         <v>168</v>
@@ -25162,10 +25182,10 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>728</v>
+        <v>736</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>612</v>
+        <v>620</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -25191,16 +25211,16 @@
         <v>172</v>
       </c>
       <c r="L193" t="s" s="2">
-        <v>613</v>
+        <v>621</v>
       </c>
       <c r="M193" t="s" s="2">
-        <v>614</v>
+        <v>622</v>
       </c>
       <c r="N193" t="s" s="2">
-        <v>615</v>
+        <v>623</v>
       </c>
       <c r="O193" t="s" s="2">
-        <v>616</v>
+        <v>624</v>
       </c>
       <c r="P193" t="s" s="2">
         <v>82</v>
@@ -25228,10 +25248,10 @@
         <v>115</v>
       </c>
       <c r="Y193" t="s" s="2">
-        <v>617</v>
+        <v>625</v>
       </c>
       <c r="Z193" t="s" s="2">
-        <v>618</v>
+        <v>626</v>
       </c>
       <c r="AA193" t="s" s="2">
         <v>82</v>
@@ -25249,7 +25269,7 @@
         <v>82</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>612</v>
+        <v>620</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>79</v>
@@ -25267,7 +25287,7 @@
         <v>82</v>
       </c>
       <c r="AL193" t="s" s="2">
-        <v>619</v>
+        <v>627</v>
       </c>
       <c r="AM193" t="s" s="2">
         <v>168</v>
@@ -25281,10 +25301,10 @@
     </row>
     <row r="194">
       <c r="A194" t="s" s="2">
-        <v>729</v>
+        <v>737</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>620</v>
+        <v>628</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -25307,16 +25327,16 @@
         <v>82</v>
       </c>
       <c r="K194" t="s" s="2">
-        <v>730</v>
+        <v>738</v>
       </c>
       <c r="L194" t="s" s="2">
-        <v>621</v>
+        <v>629</v>
       </c>
       <c r="M194" t="s" s="2">
-        <v>622</v>
+        <v>630</v>
       </c>
       <c r="N194" t="s" s="2">
-        <v>623</v>
+        <v>631</v>
       </c>
       <c r="O194" s="2"/>
       <c r="P194" t="s" s="2">
@@ -25366,7 +25386,7 @@
         <v>82</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>620</v>
+        <v>628</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>79</v>
@@ -25375,7 +25395,7 @@
         <v>80</v>
       </c>
       <c r="AI194" t="s" s="2">
-        <v>624</v>
+        <v>632</v>
       </c>
       <c r="AJ194" t="s" s="2">
         <v>103</v>
@@ -25384,10 +25404,10 @@
         <v>82</v>
       </c>
       <c r="AL194" t="s" s="2">
-        <v>625</v>
+        <v>633</v>
       </c>
       <c r="AM194" t="s" s="2">
-        <v>626</v>
+        <v>634</v>
       </c>
       <c r="AN194" t="s" s="2">
         <v>82</v>
@@ -25398,10 +25418,10 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>731</v>
+        <v>739</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>657</v>
+        <v>665</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -25513,10 +25533,10 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>732</v>
+        <v>740</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>659</v>
+        <v>667</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -25630,10 +25650,10 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>733</v>
+        <v>741</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>661</v>
+        <v>669</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -25659,13 +25679,13 @@
         <v>184</v>
       </c>
       <c r="L197" t="s" s="2">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="M197" t="s" s="2">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="N197" t="s" s="2">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="O197" s="2"/>
       <c r="P197" t="s" s="2">
@@ -25715,7 +25735,7 @@
         <v>82</v>
       </c>
       <c r="AF197" t="s" s="2">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="AG197" t="s" s="2">
         <v>79</v>
@@ -25724,7 +25744,7 @@
         <v>92</v>
       </c>
       <c r="AI197" t="s" s="2">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="AJ197" t="s" s="2">
         <v>103</v>
@@ -25747,10 +25767,10 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>734</v>
+        <v>742</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>663</v>
+        <v>671</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -25776,13 +25796,13 @@
         <v>105</v>
       </c>
       <c r="L198" t="s" s="2">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="M198" t="s" s="2">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="N198" t="s" s="2">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="O198" s="2"/>
       <c r="P198" t="s" s="2">
@@ -25808,13 +25828,13 @@
         <v>82</v>
       </c>
       <c r="X198" t="s" s="2">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="Y198" t="s" s="2">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="Z198" t="s" s="2">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="AA198" t="s" s="2">
         <v>82</v>
@@ -25832,7 +25852,7 @@
         <v>82</v>
       </c>
       <c r="AF198" t="s" s="2">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="AG198" t="s" s="2">
         <v>79</v>
@@ -25864,10 +25884,10 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>735</v>
+        <v>743</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>665</v>
+        <v>673</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -25893,13 +25913,13 @@
         <v>149</v>
       </c>
       <c r="L199" t="s" s="2">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="M199" t="s" s="2">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="N199" t="s" s="2">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="O199" s="2"/>
       <c r="P199" t="s" s="2">
@@ -25949,7 +25969,7 @@
         <v>82</v>
       </c>
       <c r="AF199" t="s" s="2">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="AG199" t="s" s="2">
         <v>79</v>
@@ -25967,7 +25987,7 @@
         <v>82</v>
       </c>
       <c r="AL199" t="s" s="2">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="AM199" t="s" s="2">
         <v>82</v>
@@ -25981,10 +26001,10 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>736</v>
+        <v>744</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>667</v>
+        <v>675</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -26010,13 +26030,13 @@
         <v>184</v>
       </c>
       <c r="L200" t="s" s="2">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="M200" t="s" s="2">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="N200" t="s" s="2">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="O200" s="2"/>
       <c r="P200" t="s" s="2">
@@ -26066,7 +26086,7 @@
         <v>82</v>
       </c>
       <c r="AF200" t="s" s="2">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="AG200" t="s" s="2">
         <v>79</v>
@@ -26098,10 +26118,10 @@
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>737</v>
+        <v>745</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>627</v>
+        <v>635</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -26127,16 +26147,16 @@
         <v>172</v>
       </c>
       <c r="L201" t="s" s="2">
-        <v>628</v>
+        <v>636</v>
       </c>
       <c r="M201" t="s" s="2">
-        <v>629</v>
+        <v>637</v>
       </c>
       <c r="N201" t="s" s="2">
-        <v>630</v>
+        <v>638</v>
       </c>
       <c r="O201" t="s" s="2">
-        <v>631</v>
+        <v>639</v>
       </c>
       <c r="P201" t="s" s="2">
         <v>82</v>
@@ -26164,37 +26184,37 @@
         <v>115</v>
       </c>
       <c r="Y201" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="Z201" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="AA201" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB201" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC201" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD201" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE201" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF201" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="AG201" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH201" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI201" t="s" s="2">
         <v>632</v>
-      </c>
-      <c r="Z201" t="s" s="2">
-        <v>633</v>
-      </c>
-      <c r="AA201" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB201" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC201" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD201" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE201" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF201" t="s" s="2">
-        <v>627</v>
-      </c>
-      <c r="AG201" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH201" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI201" t="s" s="2">
-        <v>624</v>
       </c>
       <c r="AJ201" t="s" s="2">
         <v>103</v>
@@ -26203,7 +26223,7 @@
         <v>82</v>
       </c>
       <c r="AL201" t="s" s="2">
-        <v>634</v>
+        <v>642</v>
       </c>
       <c r="AM201" t="s" s="2">
         <v>168</v>
@@ -26217,10 +26237,10 @@
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
-        <v>738</v>
+        <v>746</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>635</v>
+        <v>643</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
@@ -26246,13 +26266,13 @@
         <v>82</v>
       </c>
       <c r="L202" t="s" s="2">
-        <v>636</v>
+        <v>644</v>
       </c>
       <c r="M202" t="s" s="2">
-        <v>637</v>
+        <v>645</v>
       </c>
       <c r="N202" t="s" s="2">
-        <v>638</v>
+        <v>646</v>
       </c>
       <c r="O202" s="2"/>
       <c r="P202" t="s" s="2">
@@ -26302,7 +26322,7 @@
         <v>82</v>
       </c>
       <c r="AF202" t="s" s="2">
-        <v>635</v>
+        <v>643</v>
       </c>
       <c r="AG202" t="s" s="2">
         <v>79</v>
@@ -26311,7 +26331,7 @@
         <v>80</v>
       </c>
       <c r="AI202" t="s" s="2">
-        <v>602</v>
+        <v>610</v>
       </c>
       <c r="AJ202" t="s" s="2">
         <v>103</v>
@@ -26320,10 +26340,10 @@
         <v>82</v>
       </c>
       <c r="AL202" t="s" s="2">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="AM202" t="s" s="2">
-        <v>639</v>
+        <v>647</v>
       </c>
       <c r="AN202" t="s" s="2">
         <v>82</v>
